--- a/data-raw/HarmonizedTraitDefinition.xlsx
+++ b/data-raw/HarmonizedTraitDefinition.xlsx
@@ -1915,7 +1915,9 @@
       <c r="G39" s="3"/>
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
-      <c r="J39" s="3"/>
+      <c r="J39" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="40" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">

--- a/data-raw/HarmonizedTraitDefinition.xlsx
+++ b/data-raw/HarmonizedTraitDefinition.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="250">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="439" uniqueCount="252">
   <si>
     <t xml:space="preserve">Definition</t>
   </si>
@@ -490,7 +490,7 @@
     <t xml:space="preserve">Nfineroot</t>
   </si>
   <si>
-    <t xml:space="preserve">Maximum stem-specific hydraulic conductivity</t>
+    <t xml:space="preserve">Maximum sapwood-specific stem/branch hydraulic conductivity</t>
   </si>
   <si>
     <t xml:space="preserve">Ks</t>
@@ -499,13 +499,19 @@
     <t xml:space="preserve">kg m-1 MPa-1 s-1</t>
   </si>
   <si>
-    <t xml:space="preserve">Maximum leaf-specific hydraulic conductivity (Ks*Hv)</t>
+    <t xml:space="preserve">Maximum leaf-specific stem/branch hydraulic conductivity (Ks*Hv)</t>
   </si>
   <si>
     <t xml:space="preserve">Kl</t>
   </si>
   <si>
     <t xml:space="preserve">10-4 kg m-1 MPa-1 s-1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Maximum sapwood-specific root hydraulic conductivity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kr</t>
   </si>
   <si>
     <t xml:space="preserve">Maximum leaf hydraulic conductance (per leaf area)</t>
@@ -1060,7 +1066,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J1040"/>
+  <dimension ref="A1:J1041"/>
   <sheetFormatPr defaultColWidth="12.77734375" defaultRowHeight="12.8" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="111.7"/>
@@ -2291,7 +2297,7 @@
         <v>22</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>154</v>
+        <v>148</v>
       </c>
       <c r="E57" s="3"/>
       <c r="F57" s="3"/>
@@ -2304,16 +2310,16 @@
     </row>
     <row r="58" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B58" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="B58" s="3" t="s">
+      <c r="C58" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D58" s="3" t="s">
         <v>156</v>
-      </c>
-      <c r="C58" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D58" s="3" t="s">
-        <v>154</v>
       </c>
       <c r="E58" s="3"/>
       <c r="F58" s="3"/>
@@ -2335,27 +2341,23 @@
         <v>22</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>115</v>
+        <v>156</v>
       </c>
       <c r="E59" s="3"/>
-      <c r="F59" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>160</v>
-      </c>
+      <c r="F59" s="3"/>
+      <c r="G59" s="3"/>
       <c r="H59" s="3"/>
-      <c r="I59" s="3"/>
-      <c r="J59" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="I59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="3"/>
     </row>
     <row r="60" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>22</v>
@@ -2365,10 +2367,10 @@
       </c>
       <c r="E60" s="3"/>
       <c r="F60" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="G60" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H60" s="3"/>
       <c r="I60" s="3"/>
@@ -2378,10 +2380,10 @@
     </row>
     <row r="61" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>22</v>
@@ -2391,10 +2393,10 @@
       </c>
       <c r="E61" s="3"/>
       <c r="F61" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="G61" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H61" s="3"/>
       <c r="I61" s="3"/>
@@ -2404,31 +2406,33 @@
     </row>
     <row r="62" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D62" s="3"/>
+      <c r="D62" s="3" t="s">
+        <v>115</v>
+      </c>
       <c r="E62" s="3"/>
       <c r="F62" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="G62" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H62" s="3"/>
-      <c r="I62" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" s="3"/>
+      <c r="I62" s="3"/>
+      <c r="J62" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="63" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="3" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>165</v>
@@ -2436,28 +2440,26 @@
       <c r="C63" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D63" s="3" t="s">
-        <v>115</v>
-      </c>
+      <c r="D63" s="3"/>
       <c r="E63" s="3"/>
       <c r="F63" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="G63" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H63" s="3"/>
-      <c r="I63" s="3"/>
-      <c r="J63" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="I63" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" s="3"/>
     </row>
     <row r="64" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>22</v>
@@ -2467,10 +2469,10 @@
       </c>
       <c r="E64" s="3"/>
       <c r="F64" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="G64" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H64" s="3"/>
       <c r="I64" s="3"/>
@@ -2480,10 +2482,10 @@
     </row>
     <row r="65" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>22</v>
@@ -2493,10 +2495,10 @@
       </c>
       <c r="E65" s="3"/>
       <c r="F65" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="G65" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H65" s="3"/>
       <c r="I65" s="3"/>
@@ -2506,31 +2508,33 @@
     </row>
     <row r="66" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D66" s="3"/>
+      <c r="D66" s="3" t="s">
+        <v>115</v>
+      </c>
       <c r="E66" s="3"/>
       <c r="F66" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="G66" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H66" s="3"/>
-      <c r="I66" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" s="3"/>
+      <c r="I66" s="3"/>
+      <c r="J66" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="67" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="3" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>170</v>
@@ -2538,28 +2542,26 @@
       <c r="C67" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D67" s="3" t="s">
-        <v>115</v>
-      </c>
+      <c r="D67" s="3"/>
       <c r="E67" s="3"/>
       <c r="F67" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="G67" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H67" s="3"/>
-      <c r="I67" s="3"/>
-      <c r="J67" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="I67" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" s="3"/>
     </row>
     <row r="68" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>22</v>
@@ -2569,10 +2571,10 @@
       </c>
       <c r="E68" s="3"/>
       <c r="F68" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="G68" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H68" s="3"/>
       <c r="I68" s="3"/>
@@ -2582,10 +2584,10 @@
     </row>
     <row r="69" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>22</v>
@@ -2595,10 +2597,10 @@
       </c>
       <c r="E69" s="3"/>
       <c r="F69" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="G69" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H69" s="3"/>
       <c r="I69" s="3"/>
@@ -2608,31 +2610,33 @@
     </row>
     <row r="70" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D70" s="3"/>
+      <c r="D70" s="3" t="s">
+        <v>115</v>
+      </c>
       <c r="E70" s="3"/>
       <c r="F70" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="G70" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H70" s="3"/>
-      <c r="I70" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J70" s="3"/>
+      <c r="I70" s="3"/>
+      <c r="J70" s="3" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="71" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="3" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>175</v>
@@ -2640,12 +2644,14 @@
       <c r="C71" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D71" s="3" t="s">
-        <v>141</v>
-      </c>
+      <c r="D71" s="3"/>
       <c r="E71" s="3"/>
-      <c r="F71" s="3"/>
-      <c r="G71" s="3"/>
+      <c r="F71" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="G71" s="3" t="s">
+        <v>162</v>
+      </c>
       <c r="H71" s="3"/>
       <c r="I71" s="3" t="n">
         <v>0</v>
@@ -2663,7 +2669,7 @@
         <v>22</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>178</v>
+        <v>141</v>
       </c>
       <c r="E72" s="3"/>
       <c r="F72" s="3"/>
@@ -2676,21 +2682,23 @@
     </row>
     <row r="73" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="B73" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="B73" s="3" t="s">
+      <c r="C73" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D73" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="C73" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D73" s="5"/>
-      <c r="E73" s="5"/>
-      <c r="F73" s="5"/>
-      <c r="G73" s="5"/>
+      <c r="E73" s="3"/>
+      <c r="F73" s="3"/>
+      <c r="G73" s="3"/>
       <c r="H73" s="3"/>
       <c r="I73" s="3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J73" s="3"/>
     </row>
@@ -2704,30 +2712,28 @@
       <c r="C74" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D74" s="5" t="s">
-        <v>183</v>
-      </c>
+      <c r="D74" s="5"/>
       <c r="E74" s="5"/>
       <c r="F74" s="5"/>
       <c r="G74" s="5"/>
       <c r="H74" s="3"/>
       <c r="I74" s="3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J74" s="3"/>
     </row>
     <row r="75" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="B75" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="B75" s="3" t="s">
+      <c r="C75" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D75" s="5" t="s">
         <v>185</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D75" s="5" t="s">
-        <v>186</v>
       </c>
       <c r="E75" s="5"/>
       <c r="F75" s="5"/>
@@ -2740,27 +2746,25 @@
     </row>
     <row r="76" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="B76" s="3" t="s">
         <v>187</v>
       </c>
-      <c r="B76" s="3" t="s">
+      <c r="C76" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D76" s="5" t="s">
         <v>188</v>
       </c>
-      <c r="C76" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D76" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="E76" s="3"/>
-      <c r="F76" s="3"/>
-      <c r="G76" s="3"/>
+      <c r="E76" s="5"/>
+      <c r="F76" s="5"/>
+      <c r="G76" s="5"/>
       <c r="H76" s="3"/>
       <c r="I76" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J76" s="3" t="n">
-        <v>100</v>
-      </c>
+      <c r="J76" s="3"/>
     </row>
     <row r="77" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="3" t="s">
@@ -2773,7 +2777,7 @@
         <v>22</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>57</v>
+        <v>180</v>
       </c>
       <c r="E77" s="3"/>
       <c r="F77" s="3"/>
@@ -2782,7 +2786,9 @@
       <c r="I77" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="J77" s="3"/>
+      <c r="J77" s="3" t="n">
+        <v>100</v>
+      </c>
     </row>
     <row r="78" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="3" t="s">
@@ -2795,7 +2801,7 @@
         <v>22</v>
       </c>
       <c r="D78" s="3" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="E78" s="3"/>
       <c r="F78" s="3"/>
@@ -2817,7 +2823,7 @@
         <v>22</v>
       </c>
       <c r="D79" s="3" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="E79" s="3"/>
       <c r="F79" s="3"/>
@@ -2861,7 +2867,7 @@
         <v>22</v>
       </c>
       <c r="D81" s="3" t="s">
-        <v>199</v>
+        <v>50</v>
       </c>
       <c r="E81" s="3"/>
       <c r="F81" s="3"/>
@@ -2874,16 +2880,16 @@
     </row>
     <row r="82" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="3" t="s">
+        <v>199</v>
+      </c>
+      <c r="B82" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="B82" s="3" t="s">
+      <c r="C82" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D82" s="3" t="s">
         <v>201</v>
-      </c>
-      <c r="C82" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D82" s="3" t="s">
-        <v>202</v>
       </c>
       <c r="E82" s="3"/>
       <c r="F82" s="3"/>
@@ -2896,16 +2902,16 @@
     </row>
     <row r="83" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="B83" s="3" t="s">
         <v>203</v>
       </c>
-      <c r="B83" s="3" t="s">
+      <c r="C83" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D83" s="3" t="s">
         <v>204</v>
-      </c>
-      <c r="C83" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D83" s="3" t="s">
-        <v>66</v>
       </c>
       <c r="E83" s="3"/>
       <c r="F83" s="3"/>
@@ -2927,7 +2933,7 @@
         <v>22</v>
       </c>
       <c r="D84" s="3" t="s">
-        <v>207</v>
+        <v>66</v>
       </c>
       <c r="E84" s="3"/>
       <c r="F84" s="3"/>
@@ -2940,20 +2946,24 @@
     </row>
     <row r="85" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="3" t="s">
+        <v>207</v>
+      </c>
+      <c r="B85" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="B85" s="3" t="s">
+      <c r="C85" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D85" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="C85" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D85" s="3"/>
       <c r="E85" s="3"/>
       <c r="F85" s="3"/>
       <c r="G85" s="3"/>
       <c r="H85" s="3"/>
-      <c r="I85" s="3"/>
+      <c r="I85" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="J85" s="3"/>
     </row>
     <row r="86" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -2984,9 +2994,7 @@
       <c r="C87" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="D87" s="3" t="s">
-        <v>214</v>
-      </c>
+      <c r="D87" s="3"/>
       <c r="E87" s="3"/>
       <c r="F87" s="3"/>
       <c r="G87" s="3"/>
@@ -2996,38 +3004,36 @@
     </row>
     <row r="88" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="3" t="s">
+        <v>214</v>
+      </c>
+      <c r="B88" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="B88" s="3" t="s">
+      <c r="C88" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D88" s="3" t="s">
         <v>216</v>
-      </c>
-      <c r="C88" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D88" s="3" t="s">
-        <v>217</v>
       </c>
       <c r="E88" s="3"/>
       <c r="F88" s="3"/>
       <c r="G88" s="3"/>
       <c r="H88" s="3"/>
-      <c r="I88" s="3" t="n">
-        <v>0</v>
-      </c>
+      <c r="I88" s="3"/>
       <c r="J88" s="3"/>
     </row>
     <row r="89" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="B89" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="B89" s="3" t="s">
+      <c r="C89" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D89" s="3" t="s">
         <v>219</v>
-      </c>
-      <c r="C89" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D89" s="3" t="s">
-        <v>217</v>
       </c>
       <c r="E89" s="3"/>
       <c r="F89" s="3"/>
@@ -3049,7 +3055,7 @@
         <v>22</v>
       </c>
       <c r="D90" s="3" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E90" s="3"/>
       <c r="F90" s="3"/>
@@ -3071,7 +3077,7 @@
         <v>22</v>
       </c>
       <c r="D91" s="3" t="s">
-        <v>77</v>
+        <v>219</v>
       </c>
       <c r="E91" s="3"/>
       <c r="F91" s="3"/>
@@ -3137,27 +3143,29 @@
         <v>22</v>
       </c>
       <c r="D94" s="3" t="s">
-        <v>230</v>
+        <v>77</v>
       </c>
       <c r="E94" s="3"/>
       <c r="F94" s="3"/>
       <c r="G94" s="3"/>
       <c r="H94" s="3"/>
-      <c r="I94" s="3"/>
+      <c r="I94" s="3" t="n">
+        <v>0</v>
+      </c>
       <c r="J94" s="3"/>
     </row>
     <row r="95" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="B95" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="B95" s="3" t="s">
+      <c r="C95" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D95" s="3" t="s">
         <v>232</v>
-      </c>
-      <c r="C95" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D95" s="3" t="s">
-        <v>214</v>
       </c>
       <c r="E95" s="3"/>
       <c r="F95" s="3"/>
@@ -3177,7 +3185,7 @@
         <v>22</v>
       </c>
       <c r="D96" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E96" s="3"/>
       <c r="F96" s="3"/>
@@ -3197,7 +3205,7 @@
         <v>22</v>
       </c>
       <c r="D97" s="3" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E97" s="3"/>
       <c r="F97" s="3"/>
@@ -3217,7 +3225,7 @@
         <v>22</v>
       </c>
       <c r="D98" s="3" t="s">
-        <v>239</v>
+        <v>216</v>
       </c>
       <c r="E98" s="3"/>
       <c r="F98" s="3"/>
@@ -3228,16 +3236,16 @@
     </row>
     <row r="99" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B99" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="B99" s="3" t="s">
+      <c r="C99" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D99" s="3" t="s">
         <v>241</v>
-      </c>
-      <c r="C99" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="D99" s="3" t="s">
-        <v>214</v>
       </c>
       <c r="E99" s="3"/>
       <c r="F99" s="3"/>
@@ -3254,38 +3262,34 @@
         <v>243</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="D100" s="3"/>
+        <v>22</v>
+      </c>
+      <c r="D100" s="3" t="s">
+        <v>216</v>
+      </c>
       <c r="E100" s="3"/>
       <c r="F100" s="3"/>
       <c r="G100" s="3"/>
-      <c r="H100" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="I100" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="J100" s="3" t="n">
-        <v>2</v>
-      </c>
+      <c r="H100" s="3"/>
+      <c r="I100" s="3"/>
+      <c r="J100" s="3"/>
     </row>
     <row r="101" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="B101" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="C101" s="3" t="s">
         <v>246</v>
-      </c>
-      <c r="B101" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="C101" s="3" t="s">
-        <v>244</v>
       </c>
       <c r="D101" s="3"/>
       <c r="E101" s="3"/>
       <c r="F101" s="3"/>
       <c r="G101" s="3"/>
       <c r="H101" s="3" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="I101" s="3" t="n">
         <v>0</v>
@@ -3302,21 +3306,44 @@
         <v>249</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>22</v>
+        <v>246</v>
       </c>
       <c r="D102" s="3"/>
       <c r="E102" s="3"/>
       <c r="F102" s="3"/>
       <c r="G102" s="3"/>
-      <c r="H102" s="3"/>
+      <c r="H102" s="3" t="s">
+        <v>247</v>
+      </c>
       <c r="I102" s="3" t="n">
         <v>0</v>
       </c>
       <c r="J102" s="3" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A103" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="B103" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="C103" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D103" s="3"/>
+      <c r="E103" s="3"/>
+      <c r="F103" s="3"/>
+      <c r="G103" s="3"/>
+      <c r="H103" s="3"/>
+      <c r="I103" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="J103" s="3" t="n">
         <v>5</v>
       </c>
     </row>
-    <row r="103" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="104" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="105" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="106" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
@@ -4254,6 +4281,7 @@
     <row r="1038" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1039" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="1040" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
+    <row r="1041" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0" footer="0"/>
